--- a/templates/33-swimlane-process-map.xlsx
+++ b/templates/33-swimlane-process-map.xlsx
@@ -282,6 +282,9 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <v>Minutes at this step</v>
+          </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="1F4E79"/>
@@ -309,6 +312,40 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Mean — anything above this line is where the time actually goes</v>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Step log'!$I$6:$I$29</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -338,6 +375,9 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -348,7 +388,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -1164,7 +1204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1175,7 +1215,6 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
@@ -1184,6 +1223,7 @@
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1263,6 +1303,11 @@
           <t>What you saw that the SOP does not say</t>
         </is>
       </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Mean minutes per step</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
@@ -1296,6 +1341,10 @@
         <v/>
       </c>
       <c r="H6" s="15" t="inlineStr"/>
+      <c r="I6" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
@@ -1333,6 +1382,10 @@
           <t>Deflection is measured as a success even when it adds a minute.</t>
         </is>
       </c>
+      <c r="I7" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
@@ -1370,6 +1423,10 @@
           <t>Wait is invisible in AHT and is most of the customer's experience.</t>
         </is>
       </c>
+      <c r="I8" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
@@ -1407,6 +1464,10 @@
           <t>Re-keyed by hand; nothing validates it.</t>
         </is>
       </c>
+      <c r="I9" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
@@ -1440,6 +1501,10 @@
         <v/>
       </c>
       <c r="H10" s="15" t="inlineStr"/>
+      <c r="I10" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
@@ -1477,6 +1542,10 @@
           <t>A number the CRM could have shown.</t>
         </is>
       </c>
+      <c r="I11" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
@@ -1514,6 +1583,10 @@
           <t>Off-system. Appears in no report. This is the rework loop.</t>
         </is>
       </c>
+      <c r="I12" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
@@ -1547,6 +1620,10 @@
         <v/>
       </c>
       <c r="H13" s="15" t="inlineStr"/>
+      <c r="I13" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
@@ -1580,6 +1657,10 @@
         <v/>
       </c>
       <c r="H14" s="15" t="inlineStr"/>
+      <c r="I14" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
@@ -1617,6 +1698,10 @@
           <t>Four hours of lead time against 19.5 minutes of touch time for the whole case. One approval is 90% of what the customer waits through.</t>
         </is>
       </c>
+      <c r="I15" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
@@ -1650,6 +1735,10 @@
         <v/>
       </c>
       <c r="H16" s="15" t="inlineStr"/>
+      <c r="I16" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
@@ -1683,6 +1772,10 @@
         <v/>
       </c>
       <c r="H17" s="15" t="inlineStr"/>
+      <c r="I17" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="n"/>
@@ -1696,6 +1789,10 @@
         <v/>
       </c>
       <c r="H18" s="17" t="n"/>
+      <c r="I18" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="n"/>
@@ -1709,6 +1806,10 @@
         <v/>
       </c>
       <c r="H19" s="17" t="n"/>
+      <c r="I19" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="n"/>
@@ -1722,6 +1823,10 @@
         <v/>
       </c>
       <c r="H20" s="17" t="n"/>
+      <c r="I20" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n"/>
@@ -1735,6 +1840,10 @@
         <v/>
       </c>
       <c r="H21" s="17" t="n"/>
+      <c r="I21" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="99" customHeight="1">
       <c r="A22" s="17" t="n"/>
@@ -1748,7 +1857,11 @@
         <v/>
       </c>
       <c r="H22" s="17" t="n"/>
-      <c r="J22" s="18" t="inlineStr">
+      <c r="I22" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
         <is>
           <t>HOW TO READ IT.  One bar dwarfs the rest, and it is not anybody working. The approval wait is 240 of the 265 minutes this case takes — 90% of what the customer lives through — against 19.5 minutes of touch time across all twelve steps. That ratio is process cycle efficiency, and 7% is normal rather than shocking, which is exactly why it is worth showing people their own.
 SO:  Attack the tallest bar, not the most annoying one. Here that means the approval step: ask what it is protecting against, what a reasonable auto-approve threshold would be, and who owns that decision. Shaving seconds off the agent's handling while a four-hour wait sits untouched is the most common way a support project produces no customer-visible change.</t>
@@ -1767,6 +1880,10 @@
         <v/>
       </c>
       <c r="H23" s="17" t="n"/>
+      <c r="I23" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="n"/>
@@ -1780,6 +1897,10 @@
         <v/>
       </c>
       <c r="H24" s="17" t="n"/>
+      <c r="I24" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n"/>
@@ -1793,6 +1914,10 @@
         <v/>
       </c>
       <c r="H25" s="17" t="n"/>
+      <c r="I25" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="n"/>
@@ -1806,6 +1931,10 @@
         <v/>
       </c>
       <c r="H26" s="17" t="n"/>
+      <c r="I26" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n"/>
@@ -1819,6 +1948,10 @@
         <v/>
       </c>
       <c r="H27" s="17" t="n"/>
+      <c r="I27" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n"/>
@@ -1832,6 +1965,10 @@
         <v/>
       </c>
       <c r="H28" s="17" t="n"/>
+      <c r="I28" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n"/>
@@ -1845,6 +1982,10 @@
         <v/>
       </c>
       <c r="H29" s="17" t="n"/>
+      <c r="I29" s="5">
+        <f>IF(COUNT($E$6:$E$29)=0,"",AVERAGE($E$6:$E$29))</f>
+        <v/>
+      </c>
     </row>
     <row r="30"/>
     <row r="31">
@@ -1977,12 +2118,12 @@
   <autoFilter ref="A5:H29"/>
   <mergeCells count="19">
     <mergeCell ref="A37:C37"/>
+    <mergeCell ref="K22:S22"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E32:H32"/>
     <mergeCell ref="E37:H37"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="J22:R22"/>
     <mergeCell ref="E33:H33"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A38:C38"/>
